--- a/docs/PENDERIE_DROITS_v2.xlsx
+++ b/docs/PENDERIE_DROITS_v2.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -661,9 +661,9 @@
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>DENIED ◆</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1086,9 +1086,9 @@
           <t>VIEW</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>EDIT ◆</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1123,9 +1123,9 @@
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>VIEW ◆</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ventes</t>
+          <t>Ventes (amis seulement, par défaut)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1165,9 +1165,9 @@
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>VIEW ◆</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1185,9 +1185,9 @@
           <t>VIEW</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>DENIED (VIEW si ouverte aux abonnés) ◆</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1329,23 +1329,31 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
+          <t>8. Prêts, ventes, catégories (06/10, aligné sur le code) : un coloc VOIT les prêts et ventes de ses colocs sans les gérer, et ne touche pas à leurs catégories. Une vente est ouverte aux amis par défaut, aux abonnés seulement si l'annonce le prévoit. Un profil +18 du foyer peut proposer une correction sur un objet vu dans un look, comme sur tout objet du foyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
           <t>Partie 4 « voler les affaires du voisin » : testée — 403 partout, aucune fuite dans les réponses.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="B23:H23"/>
